--- a/90410_REPORT_BOTTEGA_09-01-2026.xlsx
+++ b/90410_REPORT_BOTTEGA_09-01-2026.xlsx
@@ -9,13 +9,12 @@
     <sheet name="VENDUTO FASCIA ORARIA" r:id="rId3" sheetId="1"/>
     <sheet name="ANALISI ARTICOLI" r:id="rId4" sheetId="2"/>
     <sheet name="PDT VENUTI FS GIORNALIERO" r:id="rId5" sheetId="3"/>
-    <sheet name="INGRESSI" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="42">
   <si>
     <t>FASCIA ORARIA</t>
   </si>
@@ -50,39 +49,6 @@
     <t>15:00 - 15:59</t>
   </si>
   <si>
-    <t>16:00 - 16:59</t>
-  </si>
-  <si>
-    <t>17:00 - 17:59</t>
-  </si>
-  <si>
-    <t>18:00 - 18:59</t>
-  </si>
-  <si>
-    <t>19:00 - 19:59</t>
-  </si>
-  <si>
-    <t>20:00 - 20:59</t>
-  </si>
-  <si>
-    <t>21:00 - 21:59</t>
-  </si>
-  <si>
-    <t>22:00 - 22:59</t>
-  </si>
-  <si>
-    <t>23:00 - 23:59</t>
-  </si>
-  <si>
-    <t>0:00 - 0:59</t>
-  </si>
-  <si>
-    <t>1:00 - 1:59</t>
-  </si>
-  <si>
-    <t>2:00 - 2:59</t>
-  </si>
-  <si>
     <t>TOTALE INCASSI 09/01/2026</t>
   </si>
   <si>
@@ -119,42 +85,36 @@
     <t>Pollo intero piccolo</t>
   </si>
   <si>
+    <t>50-004-010-000160</t>
+  </si>
+  <si>
+    <t>Patate</t>
+  </si>
+  <si>
+    <t>50-004-010-000030</t>
+  </si>
+  <si>
+    <t>Tagliata di pollo</t>
+  </si>
+  <si>
+    <t>50-004-010-000190</t>
+  </si>
+  <si>
+    <t>Contorno del giorno</t>
+  </si>
+  <si>
+    <t>50-004-010-000100</t>
+  </si>
+  <si>
+    <t>Cosce di pollo</t>
+  </si>
+  <si>
     <t>50-004-010-000040</t>
   </si>
   <si>
     <t>Mezzo pollo</t>
   </si>
   <si>
-    <t>50-004-010-000160</t>
-  </si>
-  <si>
-    <t>Patate</t>
-  </si>
-  <si>
-    <t>50-004-010-000190</t>
-  </si>
-  <si>
-    <t>Contorno del giorno</t>
-  </si>
-  <si>
-    <t>50-004-010-000110</t>
-  </si>
-  <si>
-    <t>Pollo alla cacciatora + contorno</t>
-  </si>
-  <si>
-    <t>50-004-010-000030</t>
-  </si>
-  <si>
-    <t>Tagliata di pollo</t>
-  </si>
-  <si>
-    <t>50-004-010-000100</t>
-  </si>
-  <si>
-    <t>Cosce di pollo</t>
-  </si>
-  <si>
     <t>50-004-010-000380</t>
   </si>
   <si>
@@ -167,12 +127,6 @@
     <t xml:space="preserve">Menù Bimbi </t>
   </si>
   <si>
-    <t>50-004-010-000150</t>
-  </si>
-  <si>
-    <t>1/2 Pannocchia</t>
-  </si>
-  <si>
     <t>TOTALE GRUPPO</t>
   </si>
   <si>
@@ -186,21 +140,6 @@
   </si>
   <si>
     <t>12:00-15:59</t>
-  </si>
-  <si>
-    <t>16:00-18:59</t>
-  </si>
-  <si>
-    <t>19:00-02:59</t>
-  </si>
-  <si>
-    <t>09/01/2026</t>
-  </si>
-  <si>
-    <t>VAR %</t>
-  </si>
-  <si>
-    <t>10/01/2025</t>
   </si>
 </sst>
 </file>
@@ -338,7 +277,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true"/>
@@ -351,27 +290,13 @@
     <xf numFmtId="4" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.59375" customWidth="true" bestFit="true"/>
@@ -459,115 +384,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="2">
+      <c r="A11" t="s" s="1">
         <v>11</v>
       </c>
-      <c r="B11" t="n" s="5">
-        <v>0.0</v>
+      <c r="B11" t="n" s="1">
+        <v>230.23</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="4">
+      <c r="A12" t="s" s="1">
         <v>12</v>
       </c>
-      <c r="B12" t="n" s="7">
-        <v>0.0</v>
+      <c r="B12" t="n" s="1">
+        <v>198.64</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s" s="2">
+      <c r="A13" t="s" s="1">
         <v>13</v>
       </c>
-      <c r="B13" t="n" s="5">
-        <v>28.0001</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="4">
-        <v>14</v>
-      </c>
-      <c r="B14" t="n" s="7">
-        <v>65.091</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="B15" t="n" s="5">
-        <v>94.7273</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="4">
-        <v>16</v>
-      </c>
-      <c r="B16" t="n" s="7">
-        <v>8.1819</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="B17" t="n" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="4">
-        <v>18</v>
-      </c>
-      <c r="B18" t="n" s="7">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B19" t="n" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="4">
-        <v>20</v>
-      </c>
-      <c r="B20" t="n" s="7">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B21" t="n" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="1">
-        <v>22</v>
-      </c>
-      <c r="B22" t="n" s="1">
-        <v>426.23</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="1">
-        <v>23</v>
-      </c>
-      <c r="B23" t="n" s="1">
-        <v>712.2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B24" t="n" s="1">
-        <v>-40.15</v>
+      <c r="B13" t="n" s="1">
+        <v>15.9</v>
       </c>
     </row>
   </sheetData>
@@ -577,11 +414,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="30.2109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="24.109375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.81640625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="17.91796875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="7.72265625" customWidth="true" bestFit="true"/>
@@ -589,220 +426,186 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s" s="4">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n" s="7">
-        <v>265.0455</v>
+        <v>136.0455</v>
       </c>
       <c r="D2" t="n" s="7">
-        <v>23.0</v>
+        <v>12.0</v>
       </c>
       <c r="E2" t="n" s="7">
-        <v>62.18</v>
+        <v>59.09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n" s="5">
-        <v>40.7273</v>
+        <v>26.1818</v>
       </c>
       <c r="D3" t="n" s="5">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="E3" t="n" s="5">
-        <v>9.56</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n" s="7">
-        <v>27.0</v>
+        <v>13.8183</v>
       </c>
       <c r="D4" t="n" s="7">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E4" t="n" s="7">
-        <v>6.33</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C5" t="n" s="5">
-        <v>24.7275</v>
+        <v>11.7273</v>
       </c>
       <c r="D5" t="n" s="5">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="E5" t="n" s="5">
-        <v>5.8</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C6" t="n" s="7">
-        <v>18.182</v>
+        <v>9.091</v>
       </c>
       <c r="D6" t="n" s="7">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="E6" t="n" s="7">
-        <v>4.27</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C7" t="n" s="5">
-        <v>11.7273</v>
+        <v>9.0</v>
       </c>
       <c r="D7" t="n" s="5">
         <v>1.0</v>
       </c>
       <c r="E7" t="n" s="5">
-        <v>2.75</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="4">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s" s="4">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n" s="7">
-        <v>11.7273</v>
+        <v>9.0</v>
       </c>
       <c r="D8" t="n" s="7">
         <v>1.0</v>
       </c>
       <c r="E8" t="n" s="7">
-        <v>2.75</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n" s="5">
-        <v>9.0</v>
+        <v>8.1818</v>
       </c>
       <c r="D9" t="n" s="5">
         <v>1.0</v>
       </c>
       <c r="E9" t="n" s="5">
-        <v>2.11</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n" s="7">
-        <v>8.1818</v>
+        <v>7.1818</v>
       </c>
       <c r="D10" t="n" s="7">
         <v>1.0</v>
       </c>
       <c r="E10" t="n" s="7">
-        <v>1.92</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="C11" t="n" s="5">
-        <v>7.1818</v>
-      </c>
-      <c r="D11" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="E11" t="n" s="5">
-        <v>1.68</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="4">
-        <v>50</v>
-      </c>
-      <c r="B12" t="s" s="4">
-        <v>51</v>
-      </c>
-      <c r="C12" t="n" s="7">
-        <v>2.7273</v>
-      </c>
-      <c r="D12" t="n" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="E12" t="n" s="7">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="1">
-        <v>52</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" t="n" s="1">
-        <v>426.23</v>
-      </c>
-      <c r="D13" t="n" s="1">
-        <v>46.0</v>
-      </c>
-      <c r="E13" t="n" s="1">
+      <c r="A11" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" t="n" s="1">
+        <v>230.23</v>
+      </c>
+      <c r="D11" t="n" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="E11" t="n" s="1">
         <v>100.0</v>
       </c>
     </row>
@@ -813,24 +616,24 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="30.2109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="24.109375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="17.91796875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="31.40625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -838,15 +641,15 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="1">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n" s="5">
         <v>1.0</v>
@@ -857,10 +660,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n" s="7">
         <v>1.0</v>
@@ -871,10 +674,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C5" t="n" s="5">
         <v>1.0</v>
@@ -885,10 +688,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n" s="7">
         <v>1.0</v>
@@ -899,10 +702,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="1">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C7" t="n" s="1">
         <v>4.0</v>
@@ -914,15 +717,15 @@
     <row r="8"/>
     <row r="9">
       <c r="A9" t="s" s="1">
-        <v>56</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n" s="7">
         <v>11.0</v>
@@ -933,10 +736,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n" s="5">
         <v>3.0</v>
@@ -947,10 +750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n" s="7">
         <v>2.0</v>
@@ -961,10 +764,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C13" t="n" s="5">
         <v>2.0</v>
@@ -975,10 +778,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="4">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s" s="4">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C14" t="n" s="7">
         <v>1.0</v>
@@ -989,10 +792,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C15" t="n" s="5">
         <v>1.0</v>
@@ -1003,10 +806,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="4">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s" s="4">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n" s="7">
         <v>1.0</v>
@@ -1017,10 +820,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="1">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C17" t="n" s="1">
         <v>21.0</v>
@@ -1030,235 +833,13 @@
       </c>
     </row>
     <row r="18"/>
-    <row r="19">
-      <c r="A19" t="s" s="1">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="4">
-        <v>30</v>
-      </c>
-      <c r="B20" t="s" s="4">
-        <v>31</v>
-      </c>
-      <c r="C20" t="n" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="D20" t="n" s="7">
-        <v>11.7273</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="C21" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D21" t="n" s="5">
-        <v>9.0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="4">
-        <v>38</v>
-      </c>
-      <c r="B22" t="s" s="4">
-        <v>39</v>
-      </c>
-      <c r="C22" t="n" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="D22" t="n" s="7">
-        <v>4.5455</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="C23" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D23" t="n" s="5">
-        <v>2.7273</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="1">
-        <v>54</v>
-      </c>
-      <c r="B24" t="s" s="4">
-        <v>55</v>
-      </c>
-      <c r="C24" t="n" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="D24" t="n" s="1">
-        <v>28.0</v>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="s" s="1">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C27" t="n" s="5">
-        <v>10.0</v>
-      </c>
-      <c r="D27" t="n" s="5">
-        <v>117.2727</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="4">
-        <v>36</v>
-      </c>
-      <c r="B28" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="C28" t="n" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="D28" t="n" s="7">
-        <v>10.9092</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="C29" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D29" t="n" s="5">
-        <v>14.5455</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="4">
-        <v>40</v>
-      </c>
-      <c r="B30" t="s" s="4">
-        <v>41</v>
-      </c>
-      <c r="C30" t="n" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="D30" t="n" s="7">
-        <v>11.7273</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="C31" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D31" t="n" s="5">
-        <v>9.0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="4">
-        <v>38</v>
-      </c>
-      <c r="B32" t="s" s="4">
-        <v>39</v>
-      </c>
-      <c r="C32" t="n" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="D32" t="n" s="7">
-        <v>4.5455</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="1">
-        <v>54</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="C33" t="n" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="D33" t="n" s="1">
-        <v>168.0</v>
-      </c>
-    </row>
-    <row r="34"/>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="4">
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A33:B33"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="12.73046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="7.9140625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.73046875" customWidth="true" bestFit="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>59</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>60</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n" s="9">
-        <v>2856.0</v>
-      </c>
-      <c r="B2" s="12" t="n">
-        <f>(A2-C2)/C2</f>
-        <v>0.0</v>
-      </c>
-      <c r="C2" t="n" s="9">
-        <v>3342.0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>